--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260909.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260909.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>301,003,890</t>
+          <t>69,380,406</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>71,052,072</t>
+          <t>301,003,890</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>44,952,407</t>
+          <t>71,052,072</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>69,380,406</t>
+          <t>44,952,407</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>113,722,628</t>
+          <t>1,309,749</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,895,433</t>
+          <t>17,514,764</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,309,749</t>
+          <t>113,722,628</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>17,514,764</t>
+          <t>7,895,433</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>4,923,741</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>4,923,741</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
